--- a/missing_structure_analysis.xlsx
+++ b/missing_structure_analysis.xlsx
@@ -1007,42 +1007,67 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://www.kogas-tech.or.kr/</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://www.kogas-tech.or.kr/ | https://www.kogas-tech.or.kr/notice | https://www.kogas-tech.or.kr/notices | https://www.kogas-tech.or.kr/news | https://www.kogas-tech.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -1804,42 +1829,67 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>http://www.nims.re.kr/</t>
+          <t>https://www.nims.re.kr/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1431</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>/noticeyard/post/notification | /noticeyard/post/recruit | /noticeyard/post/bidding | /promote/post/news | /noticeyard/post/notification/35442</t>
+        </is>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NIMS 소식 → https://www.nims.re.kr/promote/post/news | 알림마당 → https://www.nims.re.kr/noticeYard/post/notification | 채용공고 → https://www.nims.re.kr/noticeYard/post/recruit | 입찰공고 → https://www.nims.re.kr/noticeYard/post/bidding | 2026년 제2분기 친인척 채용인원 공지 → https://www.nims.re.kr/noticeYard/post/notification/35442</t>
         </is>
       </c>
     </row>
@@ -2062,67 +2112,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>https://www.sciencecenter.or.kr/ | https://www.sciencecenter.or.kr/notice | https://www.sciencecenter.or.kr/notices | https://www.sciencecenter.or.kr/news | https://www.sciencecenter.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -2576,67 +2601,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>Timeout</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>https://www.kosm.or.kr/ | https://www.kosm.or.kr/notice | https://www.kosm.or.kr/notices | https://www.kosm.or.kr/news | https://www.kosm.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3398,42 +3398,67 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>http://www.kalis.or.kr/</t>
+          <t>https://www.kalis.or.kr/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>ClientOSError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>ClientOSError</t>
+        <v>20</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.kalis.or.kr/ | https://www.kalis.or.kr/notice | https://www.kalis.or.kr/notices | https://www.kalis.or.kr/news | https://www.kalis.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3857,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3845,7 +3870,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -3991,42 +4016,67 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.sports.or.kr/</t>
+          <t>https://www.sports.or.kr/sports/main/main.do</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>6732</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>게시물 상세 후보만 발견</t>
+        </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>게시판 목록보다 게시물 상세 URL 구조가 먼저 노출되는 사이트</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>게시물 상세 URL에서 상위 게시판 URL 역추적</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://www.sports.or.kr/sports/main/main.do | https://www.sports.or.kr/sports/main/contents.do?menuNo=200269 | https://www.sports.or.kr/sports/bbs/BMSR00018/list.do?menuNo=200019 | https://www.sports.or.kr/sports/bbs/BMSR00011/list.do?menuNo=200040 | https://www.sports.or.kr/sports/bbs/BMSR00036/list.do?menuNo=200043</t>
         </is>
       </c>
     </row>
@@ -4120,42 +4170,67 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>https://www.dirams.re.kr/</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>JavaScript 기반 동적 메뉴/게시판 사용 가능성</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>API/AJAX 호출 URL 또는 렌더링된 페이지 구조 별도 분석</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://www.dirams.re.kr/ | https://www.dirams.re.kr/notice | https://www.dirams.re.kr/notices | https://www.dirams.re.kr/news | https://www.dirams.re.kr/board</t>
         </is>
       </c>
     </row>
@@ -4557,42 +4632,67 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>https://www.kinfa.or.kr/</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://www.kinfa.or.kr/ | https://www.kinfa.or.kr/common/error.jsp | https://www.kinfa.or.kr/common/error.jsp | https://www.kinfa.or.kr/common/error.jsp | https://www.kinfa.or.kr/common/error.jsp</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4736,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4665,7 +4765,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4686,42 +4786,67 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>https://www.kriso.re.kr/</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>2928</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>/board.es</t>
+        </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>채용공고 바로가기 → https://www.kriso.re.kr/board.es?mid=a10402030000&amp;bid=0012</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4919,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4846,7 +4971,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5252,42 +5377,67 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://www.kofic.or.kr/ | https://www.kofic.or.kr/notice | https://www.kofic.or.kr/notices | https://www.kofic.or.kr/news | https://www.kofic.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5847,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.koref.or.kr/web/user/main.do;jsessionid=F8B1962342CD7AFD608C037C6CB5F31C</t>
+          <t>https://www.koref.or.kr/web/user/main.do;jsessionid=E757853D96103A58443E5FE6D4EDCDB3</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -6263,7 +6413,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/intro/intro.html</t>
+          <t>https://www.kosmes.or.kr/</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6315,7 +6465,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/intro/intro.html | https://www.kosmes.or.kr/intro/intro.html/notice | https://www.kosmes.or.kr/intro/intro.html/notices | https://www.kosmes.or.kr/intro/intro.html/news | https://www.kosmes.or.kr/intro/intro.html/board</t>
+          <t>https://www.kosmes.or.kr/ | https://www.kosmes.or.kr/notice | https://www.kosmes.or.kr/notices | https://www.kosmes.or.kr/news | https://www.kosmes.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -6846,42 +6996,67 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.khepi.or.kr/</t>
+          <t>https://www.khepi.or.kr/kps</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>K2Web, Joomla</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>687</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>/survey | /board</t>
+        </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>설문조사 → https://www.khepi.or.kr/survey?menuId=MENU01064 | 입찰정보 → https://www.khepi.or.kr/board?menuId=MENU00932&amp;siteId=null-</t>
         </is>
       </c>
     </row>
@@ -7566,42 +7741,67 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>https://www.kmiti.or.kr/</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>3124</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>/kr/board/kmi_notice/boardlist.do | /kr/board/kmi_data/boardlist.do | /kr/board/integrity_01/boardlist.do</t>
+        </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>알림 · 자료 → https://www.kmiti.or.kr/kr/board/kmi_notice/boardList.do | 자료 → https://www.kmiti.or.kr/kr/board/kmi_data/boardList.do | 반부패 청렴자료 → https://www.kmiti.or.kr/kr/board/integrity_01/boardList.do</t>
         </is>
       </c>
     </row>
@@ -7799,36 +7999,36 @@
         </is>
       </c>
       <c r="I104" t="n">
+        <v>18</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
         <v>19</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>20</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -8390,67 +8590,42 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://drugfree.or.kr/</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>https://drugfree.or.kr/ | https://drugfree.or.kr/notice | https://drugfree.or.kr/notices | https://drugfree.or.kr/news | https://drugfree.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -8467,67 +8642,42 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>http://www.kcti.re.kr/</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>JavaScript 기반 동적 메뉴/게시판 사용 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>API/AJAX 호출 URL 또는 렌더링된 페이지 구조 별도 분석</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1 | https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1/notice | https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1/notices | https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1/news | https://www.kcti.re.kr/web/user/main.do;jsessionid=E54DEAAC320D02CA46BEAF7728467FA1/board</t>
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9298,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>일반 HTML/미확인</t>
+          <t>Drupal, WordPress, Joomla</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9182,12 +9332,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>게시판 구조 확인 필요</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>사이트별 URL 구조를 개별 분석하여 공략</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9418,67 +9568,42 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>https://www.fowi.or.kr/</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>https://www.fowi.or.kr/ | https://www.fowi.or.kr/notice | https://www.fowi.or.kr/notices | https://www.fowi.or.kr/news | https://www.fowi.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9925,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>Timeout</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -9813,7 +9938,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>Timeout</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10473,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -10371,7 +10496,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10400,7 +10525,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -10473,67 +10598,42 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>https://www.kospole.co.kr/</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>3</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>/toto/board/careers | /toto/board/bidding | /toto/board/pr</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>5</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>게시판 후보 발견</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>채용공고 → https://www.kospole.co.kr/toto/board/careers | 입찰공고 → https://www.kospole.co.kr/toto/board/bidding | 공지사항 → https://www.kospole.co.kr/toto/board/pr</t>
+        <v>0</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10710,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>https://home.koelsa.or.kr/main.do | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=158&amp;mId=0404020000&amp;token=1789549842339 | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=131&amp;mId=0204000000&amp;token=1641740249501 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15225 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15186</t>
+          <t>https://home.koelsa.or.kr/main.do | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=158&amp;mId=0404020000&amp;token=1789552656475 | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=131&amp;mId=0204000000&amp;token=1641740249501 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15225 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15186</t>
         </is>
       </c>
     </row>
@@ -10781,67 +10881,42 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.kigepe.or.kr/kor/index.do</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>K2Web</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>http://www.kigepe.or.kr/</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1316</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L146" t="n">
-        <v>32</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>게시물 상세 후보만 발견</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>게시판 목록보다 게시물 상세 URL 구조가 먼저 노출되는 사이트</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>게시물 상세 URL에서 상위 게시판 URL 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>https://www.kigepe.or.kr/kor/index.do | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000001&amp;menuNo=13100 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000001&amp;menuNo=13100 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000034&amp;menuNo=13400 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000032&amp;menuNo=13200</t>
+        <v>0</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11349,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -11682,7 +11757,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12606,67 +12681,42 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>https://info.korail.com/</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L171" t="n">
         <v>0</v>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>Timeout</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>https://info.korail.com/ | https://info.korail.com/notice | https://info.korail.com/notices | https://info.korail.com/news | https://info.korail.com/board</t>
+        <v>0</v>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Timeout</t>
         </is>
       </c>
     </row>
@@ -13326,67 +13376,42 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>https://www.keci.or.kr/</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L181" t="n">
         <v>0</v>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>https://www.keci.or.kr/ | https://www.keci.or.kr/notice | https://www.keci.or.kr/notices | https://www.keci.or.kr/news | https://www.keci.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>

--- a/missing_structure_analysis.xlsx
+++ b/missing_structure_analysis.xlsx
@@ -647,42 +647,67 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>http://www.poma.or.kr/</t>
+          <t>https://www.poma.or.kr/poma/index.do</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>K2Web</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>있음(1개): https://www.google.com/maps/embed?pb=!1m18!1m12!1m3!1d3163.755389017443!2d127.08757067726972!3d37.53726307204635!2m3!1f0!2f0!3f0!3m2!1i1024!2i768!4f13.1!3m3!1m2!1s0x357ca523a56922ad%3A0x7554a1df7cd58b00!2z7ISc7Jq47Yq567OE7IucIOq0keynhOq1rCDqsJXrs4Dsl63roZwgMg!5e0!3m2!1sko!2skr!4v1703165362965!5m2!1sko!2skr</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>중간</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2296</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>/poma/notice.do | /poma/sidewalk.do</t>
+        </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>POMA 소식 → https://www.poma.or.kr/poma/notice.do | 보도자료실 → https://www.poma.or.kr/poma/sidewalk.do</t>
         </is>
       </c>
     </row>
@@ -1983,42 +2008,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.kr.or.kr/</t>
+          <t>https://www.kr.or.kr/main.do</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>중간</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2748</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>게시물 상세 후보만 발견</t>
+        </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>게시판 목록보다 게시물 상세 URL 구조가 먼저 노출되는 사이트</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>게시물 상세 URL에서 상위 게시판 URL 역추적</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://www.kr.or.kr/main.do | https://www.kr.or.kr/sub/info.do?m=030101 | https://www.kr.or.kr/sub/info.do?m=091001 | https://www.kr.or.kr/sub/info.do?m=09010102 | https://www.kr.or.kr/sub/info.do?m=090501</t>
         </is>
       </c>
     </row>
@@ -2112,42 +2162,67 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://www.sciencecenter.or.kr/ | https://www.sciencecenter.or.kr/notice | https://www.sciencecenter.or.kr/notices | https://www.sciencecenter.or.kr/news | https://www.sciencecenter.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -2601,42 +2676,67 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://www.kosm.or.kr/ | https://www.kosm.or.kr/notice | https://www.kosm.or.kr/notices | https://www.kosm.or.kr/news | https://www.kosm.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3169,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3629,42 +3729,67 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.kibo.or.kr/</t>
+          <t>https://www.kibo.or.kr/index.do</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>/main/board/boardtype01.do | /main/board/boardtype301.do | /main/index.do | /main/board/boardtype107.do | /main/board/boardtype38.do</t>
+        </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>17</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>대표누리집 기술보증기금 # 기금소개 # 기보뉴스 # 채용정보 # 발간자료 # 기금소개 # 기보뉴스 # 채용정보 # 발간자료 → https://www.kibo.or.kr/main/index.do | 채용안내 → https://www.kibo.or.kr/main/board/boardType107.do | 채용공고 → https://www.kibo.or.kr/main/board/boardType38.do | 친인척 채용정보 공개 → https://www.kibo.or.kr/main/board/boardType39.do | 소식·자료 → https://www.kibo.or.kr/main/board/boardType01.do</t>
         </is>
       </c>
     </row>
@@ -3835,42 +3960,67 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>https://www.klac.or.kr/</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3927</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>/notification/notice/selectnoticelist.do | /notification/newsletterlist.do</t>
+        </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>공지사항 → https://www.klac.or.kr/notification/notice/selectNoticeList.do?boardCode=32 | e-뉴스레터(구) → https://www.klac.or.kr/notification/newsletterList.do</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4886,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4765,7 +4915,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4971,7 +5121,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5377,67 +5527,42 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>일반 HTML/미확인</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>미발견</t>
-        </is>
-      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>게시판 미발견</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
+          <t>접속 문제 해결 후 재탐색</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>https://www.kofic.or.kr/ | https://www.kofic.or.kr/notice | https://www.kofic.or.kr/notices | https://www.kofic.or.kr/news | https://www.kofic.or.kr/board</t>
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5972,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.koref.or.kr/web/user/main.do;jsessionid=E757853D96103A58443E5FE6D4EDCDB3</t>
+          <t>https://www.koref.or.kr/web/user/main.do;jsessionid=EB9EDBCDB2F0525EE1F883324DF0F26F</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -6413,7 +6538,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/</t>
+          <t>https://www.kosmes.or.kr/intro/intro.html</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6465,7 +6590,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/ | https://www.kosmes.or.kr/notice | https://www.kosmes.or.kr/notices | https://www.kosmes.or.kr/news | https://www.kosmes.or.kr/board</t>
+          <t>https://www.kosmes.or.kr/intro/intro.html | https://www.kosmes.or.kr/intro/intro.html/notice | https://www.kosmes.or.kr/intro/intro.html/notices | https://www.kosmes.or.kr/intro/intro.html/news | https://www.kosmes.or.kr/intro/intro.html/board</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8124,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8028,7 +8153,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -8590,42 +8715,67 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://drugfree.or.kr/</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>https://drugfree.or.kr/ | https://drugfree.or.kr/notice | https://drugfree.or.kr/notices | https://drugfree.or.kr/news | https://drugfree.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -8642,42 +8792,67 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>http://www.kcti.re.kr/</t>
+          <t>https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>JavaScript 기반 동적 메뉴/게시판 사용 가능성</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>API/AJAX 호출 URL 또는 렌더링된 페이지 구조 별도 분석</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6 | https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6/notice | https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6/notices | https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6/news | https://www.kcti.re.kr/web/user/main.do;jsessionid=816064AEB9C0B7F9301CD81335B0F3F6/board</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9636,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9474,7 +9649,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -9568,42 +9743,67 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>https://www.fowi.or.kr/</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>https://www.fowi.or.kr/ | https://www.fowi.or.kr/notice | https://www.fowi.or.kr/notices | https://www.fowi.or.kr/news | https://www.fowi.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -9925,7 +10125,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -9938,7 +10138,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>ConnectionError</t>
         </is>
       </c>
     </row>
@@ -10598,42 +10798,67 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>https://www.kospole.co.kr/</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>/toto/board/careers | /toto/board/bidding | /toto/board/pr</t>
+        </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>게시판 후보 발견</t>
+        </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>기존 탐색에서 게시판 후보 판정 기준 미충족 가능성</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>발견 후보를 실제 게시판인지 검증 후 boards.xlsx에 선택 등록</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>채용공고 → https://www.kospole.co.kr/toto/board/careers | 입찰공고 → https://www.kospole.co.kr/toto/board/bidding | 공지사항 → https://www.kospole.co.kr/toto/board/pr</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10935,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>https://home.koelsa.or.kr/main.do | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=158&amp;mId=0404020000&amp;token=1789552656475 | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=131&amp;mId=0204000000&amp;token=1641740249501 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15225 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15186</t>
+          <t>https://home.koelsa.or.kr/main.do | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=158&amp;mId=0404020000&amp;token=1789558223018 | https://home.koelsa.or.kr/portal/bbs/list.do?ptIdx=131&amp;mId=0204000000&amp;token=1641740249501 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15225 | https://home.koelsa.or.kr/portal/bbs/view.do?mId=0401000000&amp;ptIdx=112&amp;bIdx=15186</t>
         </is>
       </c>
     </row>
@@ -10881,42 +11106,67 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>http://www.kigepe.or.kr/</t>
+          <t>https://www.kigepe.or.kr/kor/index.do</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>K2Web</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1316</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>게시물 상세 후보만 발견</t>
+        </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 목록보다 게시물 상세 URL 구조가 먼저 노출되는 사이트</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>게시물 상세 URL에서 상위 게시판 URL 역추적</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>https://www.kigepe.or.kr/kor/index.do | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000001&amp;menuNo=13100 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000001&amp;menuNo=13100 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000034&amp;menuNo=13400 | https://www.kigepe.or.kr/user/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000032&amp;menuNo=13200</t>
         </is>
       </c>
     </row>
@@ -10933,42 +11183,67 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>https://www.fipa.or.kr/</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L147" t="n">
         <v>0</v>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>https://www.fipa.or.kr/ | https://www.fipa.or.kr/notice | https://www.fipa.or.kr/notices | https://www.fipa.or.kr/news | https://www.fipa.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11624,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -11601,15 +11876,30 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>http://www.koreajobworld.or.kr/</t>
+          <t>https://www.koreajobworld.or.kr/</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -11618,25 +11908,35 @@
       <c r="J156" t="n">
         <v>0</v>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>ConnectionError</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>ConnectionError</t>
+        <v>20</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>https://www.koreajobworld.or.kr/ | https://www.koreajobworld.or.kr/notice | https://www.koreajobworld.or.kr/notices | https://www.koreajobworld.or.kr/news | https://www.koreajobworld.or.kr/board</t>
         </is>
       </c>
     </row>
@@ -11757,7 +12057,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12681,42 +12981,67 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>https://info.korail.com/</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>일반 HTML/미확인</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>미발견</t>
+        </is>
+      </c>
       <c r="L171" t="n">
         <v>0</v>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>게시판 미발견</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>게시판 URL이 일반적인 board/bbs/notice 패턴과 다를 가능성</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>접속 문제 해결 후 재탐색</t>
+          <t>메뉴 구조와 실제 게시물 링크를 중점적으로 역추적</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>Timeout</t>
+        <v>20</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>https://info.korail.com/ | https://info.korail.com/notice | https://info.korail.com/notices | https://info.korail.com/news | https://info.korail.com/board</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13780,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8972</v>
+        <v>8970</v>
       </c>
       <c r="J182" t="n">
         <v>5</v>
@@ -13466,7 +13791,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
